--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487181_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487181_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8036</v>
+        <v>2.6743</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3203</v>
+        <v>6.6193</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.5167</v>
+        <v>-3.945</v>
       </c>
       <c r="G2" t="n">
         <v>4.7325</v>
@@ -610,13 +610,13 @@
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3992</v>
+        <v>-0.7301</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5619</v>
+        <v>-0.1391</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1626</v>
+        <v>-0.591</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9421</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9101</v>
+        <v>2.4851</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2267</v>
+        <v>4.427</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.3167</v>
+        <v>-1.9419</v>
       </c>
       <c r="G3" t="n">
         <v>2.5048</v>
@@ -688,13 +688,13 @@
         <v>1.158</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8587</v>
+        <v>-1.2836</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6993</v>
+        <v>-0.499</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1594</v>
+        <v>-0.7846</v>
       </c>
       <c r="V3" t="n">
         <v>0.1059</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8033</v>
+        <v>0.7032</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5189</v>
+        <v>3.4188</v>
       </c>
       <c r="F4" t="n">
         <v>-2.7156</v>
@@ -766,10 +766,10 @@
         <v>1.5441</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8315</v>
+        <v>-0.9317</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1361</v>
+        <v>-0.2363</v>
       </c>
       <c r="U4" t="n">
         <v>-0.6954</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DE CASTRO AYALA</t>
+          <t>P. HERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4106</v>
+        <v>-0.2125</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9307</v>
+        <v>2.8301</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3413</v>
+        <v>-3.0426</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4551</v>
+        <v>0.7407</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.595</v>
+        <v>0.4865</v>
       </c>
       <c r="I5" t="n">
-        <v>0.14</v>
+        <v>0.2542</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0814</v>
+        <v>2.1956</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3816</v>
+        <v>2.0492</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6998</v>
+        <v>0.1464</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5365</v>
+        <v>-1.4549</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.9767</v>
+        <v>-1.5627</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5598</v>
+        <v>0.1078</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3511</v>
+        <v>0.965</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3511</v>
+        <v>0.965</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8408</v>
+        <v>-1.1243</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1507</v>
+        <v>-0.2654</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6901</v>
+        <v>-0.859</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.4658</v>
+        <v>-0.794</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8999</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4658</v>
+        <v>-1.6938</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ BLANCO</t>
+          <t>A. DE CASTRO AYALA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8074</v>
+        <v>-0.4573</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5297</v>
+        <v>1.8305</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.3371</v>
+        <v>-2.2878</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7407</v>
+        <v>-0.4551</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4865</v>
+        <v>-0.595</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2542</v>
+        <v>0.14</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1956</v>
+        <v>2.0814</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0492</v>
+        <v>1.3816</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1464</v>
+        <v>0.6998</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4549</v>
+        <v>-2.5365</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5627</v>
+        <v>-1.9767</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1078</v>
+        <v>-0.5598</v>
       </c>
       <c r="P6" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.7192</v>
+        <v>-0.8874</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5658</v>
+        <v>-0.2508</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1534</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.794</v>
+        <v>-0.4658</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8999</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6938</v>
+        <v>-0.4658</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.7394</v>
+        <v>-2.2913</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3849</v>
+        <v>-0.2848</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3545</v>
+        <v>-2.0065</v>
       </c>
       <c r="G7" t="n">
         <v>-2.4769</v>
@@ -1000,13 +1000,13 @@
         <v>0.965</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4905</v>
+        <v>-1.0424</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5803</v>
+        <v>-0.4802</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9102</v>
+        <v>-0.5622</v>
       </c>
       <c r="V7" t="n">
         <v>1.228</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. POPA ANDREI</t>
+          <t>I. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.6044</v>
+        <v>-5.3382</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.6713</v>
+        <v>-2.8586</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9331</v>
+        <v>-2.4797</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.9934</v>
+        <v>-3.7869</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.0445</v>
+        <v>-1.5606</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9489</v>
+        <v>-2.2263</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.5356</v>
+        <v>-0.2959</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.1529</v>
+        <v>0.4295</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3827</v>
+        <v>-0.7254</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.4578</v>
+        <v>-3.491</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.8915</v>
+        <v>-1.9901</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5662</v>
+        <v>-1.5009</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>-0.579</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9301</v>
+        <v>1.3511</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.659</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4336</v>
+        <v>-0.6325</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2254</v>
+        <v>-0.3398</v>
       </c>
       <c r="V8" t="n">
-        <v>1.048</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. HANSEN GUTIERREZ</t>
+          <t>S. POPA ANDREI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.6456</v>
+        <v>-5.8919</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0589</v>
+        <v>-3.7715</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5867</v>
+        <v>-2.1205</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.7869</v>
+        <v>-5.9934</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5606</v>
+        <v>-5.0445</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2263</v>
+        <v>-0.9489</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2959</v>
+        <v>-2.5356</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4295</v>
+        <v>-2.1529</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7254</v>
+        <v>-0.3827</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.491</v>
+        <v>-3.4578</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.9901</v>
+        <v>-2.8915</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.5009</v>
+        <v>-0.5662</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.579</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3511</v>
+        <v>1.9301</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2797</v>
+        <v>-0.9465</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8328</v>
+        <v>-0.5337</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4468</v>
+        <v>-0.4128</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.048</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.016</v>
+        <v>-7.3778</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0353</v>
+        <v>-3.835</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9807</v>
+        <v>-3.5428</v>
       </c>
       <c r="G10" t="n">
         <v>-4.6204</v>
@@ -1234,13 +1234,13 @@
         <v>0.772</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2532</v>
+        <v>-0.6151</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8183</v>
+        <v>-0.618</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5651</v>
+        <v>0.0029</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9843</v>
@@ -1270,7 +1270,7 @@
         <v>-15.7064</v>
       </c>
       <c r="E11" t="n">
-        <v>8.375900000000001</v>
+        <v>8.375799999999998</v>
       </c>
       <c r="F11" t="n">
         <v>-24.0824</v>
@@ -1282,13 +1282,13 @@
         <v>-11.5187</v>
       </c>
       <c r="I11" t="n">
-        <v>4.1021</v>
+        <v>4.102100000000001</v>
       </c>
       <c r="J11" t="n">
         <v>17.3126</v>
       </c>
       <c r="K11" t="n">
-        <v>6.2452</v>
+        <v>6.245199999999999</v>
       </c>
       <c r="L11" t="n">
         <v>11.0676</v>
@@ -1318,13 +1318,13 @@
         <v>-3.655</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.878200000000001</v>
+        <v>-4.878499999999999</v>
       </c>
       <c r="V11" t="n">
         <v>0.2437</v>
       </c>
       <c r="W11" t="n">
-        <v>6.2991</v>
+        <v>6.299099999999999</v>
       </c>
       <c r="X11" t="n">
         <v>-6.0554</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.5129</v>
+        <v>8.8254</v>
       </c>
       <c r="E12" t="n">
-        <v>10.2383</v>
+        <v>9.337</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7254</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>6.674</v>
@@ -1390,13 +1390,13 @@
         <v>1.5441</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9969</v>
+        <v>1.3094</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8521</v>
+        <v>0.9509</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1447</v>
+        <v>0.3586</v>
       </c>
       <c r="V12" t="n">
         <v>1.228</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4753</v>
+        <v>4.3038</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0795</v>
+        <v>6.48</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6042</v>
+        <v>-2.1762</v>
       </c>
       <c r="G13" t="n">
         <v>3.3355</v>
@@ -1468,13 +1468,13 @@
         <v>0.772</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0469</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0873</v>
+        <v>0.4878</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0403</v>
+        <v>0.3876</v>
       </c>
       <c r="V13" t="n">
         <v>0.2859</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9635</v>
+        <v>3.8109</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8427</v>
+        <v>4.7439</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8792</v>
+        <v>-0.9331</v>
       </c>
       <c r="G14" t="n">
         <v>3.0392</v>
@@ -1546,13 +1546,13 @@
         <v>0.772</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1686</v>
+        <v>0.6788</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6993</v>
+        <v>0.202</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.4769</v>
       </c>
       <c r="V14" t="n">
         <v>0.2859</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. REYES ABAD</t>
+          <t>J. OTERO GONZALEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3447</v>
+        <v>1.0397</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4664</v>
+        <v>2.9814</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1218</v>
+        <v>-1.9417</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.6915</v>
+        <v>-1.7992</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.2845</v>
+        <v>-0.6697</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.407</v>
+        <v>-1.1296</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0165</v>
+        <v>1.4702</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6833</v>
+        <v>0.6726</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6998</v>
+        <v>0.7976</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7079</v>
+        <v>-3.2694</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6012</v>
+        <v>-1.3423</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1067</v>
+        <v>-1.9272</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9301</v>
+        <v>1.7371</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9301</v>
+        <v>1.7371</v>
       </c>
       <c r="S15" t="n">
-        <v>2.948</v>
+        <v>1.1019</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7781</v>
+        <v>0.2833</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1699</v>
+        <v>0.8186</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.842</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3281</v>
+        <v>1.228</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.5138</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. OTERO GONZALEZ</t>
+          <t>A. REYES ABAD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2472</v>
+        <v>0.456</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0816</v>
+        <v>0.7655</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8343</v>
+        <v>-0.3095</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.7992</v>
+        <v>-1.6915</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6697</v>
+        <v>-1.2845</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1296</v>
+        <v>-0.407</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4702</v>
+        <v>0.0165</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6726</v>
+        <v>-0.6833</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7976</v>
+        <v>0.6998</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.2694</v>
+        <v>-1.7079</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3423</v>
+        <v>-0.6012</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9272</v>
+        <v>-1.1067</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3094</v>
+        <v>2.0593</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3834</v>
+        <v>1.0771</v>
       </c>
       <c r="U16" t="n">
-        <v>0.926</v>
+        <v>0.9822</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.842</v>
       </c>
       <c r="W16" t="n">
-        <v>1.228</v>
+        <v>-0.3281</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.228</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. HERNANDEZ HERNANDEZ</t>
+          <t>A. REY GUTIERREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9545</v>
+        <v>0.3084</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5825</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.372</v>
+        <v>0.3914</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0778</v>
+        <v>0.0264</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3667</v>
+        <v>1.5452</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-1.5187</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4167</v>
+        <v>1.307</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2946</v>
+        <v>1.8525</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1221</v>
+        <v>-0.5455</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4945</v>
+        <v>-1.2805</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6612</v>
+        <v>-0.3073</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8333</v>
+        <v>-0.9732</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.158</v>
+        <v>-0.386</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>0.772</v>
+        <v>1.5441</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9202</v>
+        <v>1.2397</v>
       </c>
       <c r="T17" t="n">
-        <v>1.482</v>
+        <v>0.54</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4382</v>
+        <v>0.6996</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2702</v>
+        <v>-0.5717</v>
       </c>
       <c r="W17" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6562</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. REY GUTIERREZ</t>
+          <t>O. HERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.509</v>
+        <v>0.2066</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1172</v>
+        <v>-0.2186</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3918</v>
+        <v>0.4252</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0264</v>
+        <v>-1.0778</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5452</v>
+        <v>-0.3667</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5187</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>1.307</v>
+        <v>0.4167</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8525</v>
+        <v>0.2946</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5455</v>
+        <v>0.1221</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2805</v>
+        <v>-1.4945</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3073</v>
+        <v>-0.6612</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9732</v>
+        <v>-0.8333</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.386</v>
+        <v>-1.158</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5441</v>
+        <v>0.772</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4403</v>
+        <v>1.1723</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7403</v>
+        <v>0.6808</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7</v>
+        <v>0.4914</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5717</v>
+        <v>1.2702</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5717</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0147</v>
+        <v>-0.0745</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8953</v>
+        <v>0.5949</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.91</v>
+        <v>-0.6694</v>
       </c>
       <c r="G19" t="n">
         <v>0.6673</v>
@@ -1936,13 +1936,13 @@
         <v>0.193</v>
       </c>
       <c r="S19" t="n">
-        <v>0.353</v>
+        <v>0.2931</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5486</v>
+        <v>0.2482</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1957</v>
+        <v>0.0449</v>
       </c>
       <c r="V19" t="n">
         <v>-1.228</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8419</v>
+        <v>-0.7595</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4789</v>
+        <v>-0.8781</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3629</v>
+        <v>0.1186</v>
       </c>
       <c r="G20" t="n">
         <v>-0.852</v>
@@ -2014,13 +2014,13 @@
         <v>0.965</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7039</v>
+        <v>0.3784</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4019</v>
+        <v>0.199</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3021</v>
+        <v>0.1794</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2859</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.444</v>
+        <v>-1.0751</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7422</v>
+        <v>0.3594</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7019</v>
+        <v>-1.4345</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9052</v>
@@ -2092,13 +2092,13 @@
         <v>1.3511</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6088</v>
+        <v>0.7601</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8923</v>
+        <v>0.2092</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2835</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0.614</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>15.7065</v>
+        <v>17.0417</v>
       </c>
       <c r="E22" t="n">
-        <v>24.0824</v>
+        <v>24.0823</v>
       </c>
       <c r="F22" t="n">
-        <v>-8.3759</v>
+        <v>-7.0408</v>
       </c>
       <c r="G22" t="n">
-        <v>7.4167</v>
+        <v>7.416700000000001</v>
       </c>
       <c r="H22" t="n">
         <v>11.5187</v>
@@ -2155,7 +2155,7 @@
         <v>-17.3123</v>
       </c>
       <c r="N22" t="n">
-        <v>-6.245</v>
+        <v>-6.245000000000001</v>
       </c>
       <c r="O22" t="n">
         <v>-11.0675</v>
@@ -2170,19 +2170,19 @@
         <v>11.5805</v>
       </c>
       <c r="S22" t="n">
-        <v>8.533399999999999</v>
+        <v>9.868499999999999</v>
       </c>
       <c r="T22" t="n">
         <v>4.8783</v>
       </c>
       <c r="U22" t="n">
-        <v>3.6549</v>
+        <v>4.9901</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2436000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>6.055400000000001</v>
+        <v>6.0554</v>
       </c>
       <c r="X22" t="n">
         <v>-6.2991</v>
